--- a/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Revenue/Revenue_CrossTabs_CadreDivide.xlsx
+++ b/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Revenue/Revenue_CrossTabs_CadreDivide.xlsx
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -672,27 +672,27 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3.08</v>
+        <v>4.38</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -702,27 +702,27 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
@@ -732,27 +732,27 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="7">
@@ -762,27 +762,27 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
